--- a/SampleData.xlsx
+++ b/SampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentutsedu-my.sharepoint.com/personal/amir_dashti_student_uts_edu_au/Documents/UTS PhD/Photocatalyst/Pharmaceutical Review/Data and model/experimental web validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E97B4D39-AD1A-418D-813D-73EE5BFAB8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{E97B4D39-AD1A-418D-813D-73EE5BFAB8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF77FA27-D3A0-42A6-A9CD-ACF8611C849B}"/>
   <bookViews>
     <workbookView xWindow="15636" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{D0EAE5ED-EECF-4A3D-85D0-0B69910F98F3}"/>
   </bookViews>
@@ -39,12 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>BET specific surface area (m2 g-1)</t>
-  </si>
-  <si>
-    <t>Oxidant</t>
   </si>
   <si>
     <t>Oxidant concentration (mM)</t>
@@ -458,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4668F2-E1C8-4660-8DDA-97863E02FA6A}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,9 +494,6 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
